--- a/src/attributions/attributions_ig_traj_342.xlsx
+++ b/src/attributions/attributions_ig_traj_342.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04447454703699288</v>
+        <v>0.05234436502629849</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03882842404238316</v>
+        <v>-0.05153376075751771</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0007061221678118019</v>
+        <v>-0.005644698529208104</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1023,22 +1023,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07907294127818798</v>
+        <v>0.1254051613977938</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07231692827545755</v>
+        <v>-0.1453914574260985</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01035761035387076</v>
+        <v>-0.03987296502933622</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1050,136 +1050,136 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.070661118791136</v>
+        <v>0.0492299867854185</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0190619029870412</v>
+        <v>0.00185527507724848</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04166325275798911</v>
+        <v>-0.01356597533874538</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.008697402707400144</v>
+        <v>-0.00109050888087763</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.003608802719456823</v>
+        <v>-0.03395162381656541</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.003450568411044531</v>
+        <v>0.007021466753716486</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01774201471091038</v>
+        <v>0.0918170546971746</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.05857375033418339</v>
+        <v>-0.05028501840041397</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04813487136502508</v>
+        <v>0.1397869483436359</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2900177064056594</v>
+        <v>0.316577224896616</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.01463373790542958</v>
+        <v>-0.1888084620739988</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1131682248396806</v>
+        <v>-0.0417922379446108</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02646054735778742</v>
+        <v>-0.02502388544497432</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.06223034772545567</v>
+        <v>-0.005234586710839486</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06148119271889669</v>
+        <v>-0.0168063179904836</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1191,19 +1191,19 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03469679585046096</v>
+        <v>-0.06696997286834079</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.05310925531311226</v>
+        <v>0.01487534888320436</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1283241712269217</v>
+        <v>0.05506875799155563</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1571026857500595</v>
+        <v>0.1787877285616565</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02148188848811495</v>
+        <v>-0.09687677667753607</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.07870894217708314</v>
+        <v>0.007229379169145601</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,28 +1236,28 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.05329969808525266</v>
+        <v>-0.1034089687914537</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01888702477383203</v>
+        <v>0.08897879102715546</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02401962684917283</v>
+        <v>0.004515128602235208</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
@@ -1266,25 +1266,25 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0006163234121999534</v>
+        <v>-0.00697626504980881</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.01108328353871343</v>
+        <v>0.02296294166024801</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02470272257831817</v>
+        <v>-0.004226232242684707</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,49 +1293,49 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.05078912179411951</v>
+        <v>-0.1190655554157646</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04154083301832536</v>
+        <v>0.08641991109532469</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.03098140964109593</v>
+        <v>0.0193457074520717</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.03882613937468871</v>
+        <v>-0.05418673850150756</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1554070679671568</v>
+        <v>0.02764602076819313</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.04330927605239961</v>
+        <v>-0.0603865322032609</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1350,22 +1350,22 @@
         <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01960465274571437</v>
+        <v>0.1125482401566066</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.06598078593762902</v>
+        <v>-0.07915575097546711</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.03230259921445157</v>
+        <v>0.009737387675172607</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1377,19 +1377,19 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.06949893135268641</v>
+        <v>-0.009656740597811339</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.01781363745566294</v>
+        <v>0.04737002489668396</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.006994166019795287</v>
+        <v>0.00732328188069476</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
@@ -1398,58 +1398,58 @@
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.07183845238245873</v>
+        <v>-0.06796891261033129</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.04723353086077286</v>
+        <v>0.06936553732696382</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.05058302248857639</v>
+        <v>0.04276167006934119</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.06062690088368602</v>
+        <v>-0.03233555874052658</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03953622896993633</v>
+        <v>0.01271891582745774</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.01593268895460145</v>
+        <v>-0.02598315868710384</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1458,19 +1458,19 @@
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.05752686454961884</v>
+        <v>-0.1237449750096673</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01803757489752736</v>
+        <v>0.09685469622164289</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.01943484124425855</v>
+        <v>-0.0005910633032595545</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
@@ -1482,85 +1482,85 @@
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01321443000407138</v>
+        <v>-0.0615352625038931</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.04188731037726349</v>
+        <v>0.02911362809906839</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02299931437362761</v>
+        <v>-0.006249388842992819</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.006701280575512786</v>
+        <v>-0.2062041167428514</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.06660086871083809</v>
+        <v>0.3045062242865635</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.05076426412784624</v>
+        <v>0.09547275601120833</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.03678407108532623</v>
+        <v>-0.09607389021828255</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.07142662872141697</v>
+        <v>0.0293867169496805</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1568,160 +1568,160 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.02934145018557399</v>
+        <v>-0.01824591854229486</v>
       </c>
       <c r="C3" t="n">
-        <v>5.679427942279034e-11</v>
+        <v>1.808365385143899e-11</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04232478531546931</v>
+        <v>-0.0001903432946236326</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1424494834154655</v>
+        <v>0.01380839912050056</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1533365429983102</v>
+        <v>-0.1051574070287342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0547153465892523</v>
+        <v>0.02482839067842787</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0830439537493262</v>
+        <v>0.01610426225903023</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2282739232125155</v>
+        <v>0.02752379292294672</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06439267087087099</v>
+        <v>-0.1165982830143694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1209116173652343</v>
+        <v>-0.006717862260627549</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.188553746939143</v>
+        <v>-0.07975250213648624</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08304989538177433</v>
+        <v>-0.05374027633810859</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05621881096594605</v>
+        <v>0.001796760918501322</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4.419123366927643e-11</v>
+        <v>2.827088529232274e-11</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02808392988286419</v>
+        <v>0.004378121267825821</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.01392995913961858</v>
+        <v>-0.01014312512007636</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.007368165522139576</v>
+        <v>-0.1906689239342358</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1306828104046701</v>
+        <v>-0.01552516189541674</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.10520653927451</v>
+        <v>-0.1016335474580514</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.136191401937433</v>
+        <v>-0.05339181532423267</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3419084925893642</v>
+        <v>-0.1875382510732407</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.06021398493403526</v>
+        <v>-0.04630478832119076</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.3313510803881007</v>
+        <v>-0.07891523452175057</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.3799772985749425</v>
+        <v>0.03076072062052608</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1730,55 +1730,55 @@
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.07923173135496303</v>
+        <v>-0.04350463602416864</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.07895519595174531</v>
+        <v>0.01553092872452972</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0340818679899359</v>
+        <v>0.07164629936804913</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.08628151308585062</v>
+        <v>0.03508255466972575</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1175041303607124</v>
+        <v>0.1447441461689078</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03364404676713716</v>
+        <v>0.04562918474820533</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.112617450961991</v>
+        <v>0.114588100944576</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.02461215557076772</v>
+        <v>-0.0759498543439798</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
@@ -1787,22 +1787,22 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.09741769120067671</v>
+        <v>-0.1949358576859805</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2088291804386518</v>
+        <v>-0.02373062608805759</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1548685106631699</v>
+        <v>-0.0849225863241834</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2509889714539147</v>
+        <v>0.06562750545528281</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1814,79 +1814,79 @@
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1278398348617482</v>
+        <v>0.1219774622050278</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.04166511035665107</v>
+        <v>-0.01000318039276495</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.005046869752108804</v>
+        <v>0.0250697214295019</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.1513199265102507</v>
+        <v>-0.01399854070984488</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.000214492702695937</v>
+        <v>0.006189305506984083</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.005693117737259187</v>
+        <v>0.001578380518292502</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.006331676863700559</v>
+        <v>-0.003701500214785838</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.00817541118588771</v>
+        <v>-0.005120793649004698</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1301414892725132</v>
+        <v>0.1175711647248623</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.02352025794708173</v>
+        <v>-0.02270640819277234</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0316282171965909</v>
+        <v>0.01767370829443032</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.1498466910154764</v>
+        <v>0.005325867275492885</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,160 +1895,160 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2490855992073696</v>
+        <v>0.1031235214730749</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.1033137273450801</v>
+        <v>-0.07887886763104124</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03249824945684625</v>
+        <v>-0.01696894285867714</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.1821219637017462</v>
+        <v>-0.06937030435446853</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.001292434533844702</v>
+        <v>-0.07925641979410776</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.03201410454669203</v>
+        <v>-0.0443466384056537</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.04551882764309641</v>
+        <v>0.1263649167002841</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.004807226631939897</v>
+        <v>-0.005655946302600232</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1126640529643612</v>
+        <v>0.01314980017222293</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.08068031085086334</v>
+        <v>0.08497133351994035</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.03146616368269627</v>
+        <v>0.06024486478092</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.10513614229042</v>
+        <v>0.110690590846833</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0867908252451</v>
+        <v>0.1233756417003039</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0513822924192612</v>
+        <v>0.00801363812639949</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.1300817898968938</v>
+        <v>0.01456710996378095</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0.1148931859215627</v>
+        <v>0.03372160483243633</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1043727722064847</v>
+        <v>0.09647527074753977</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.06938000084948012</v>
+        <v>0.04079057894684103</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0254460906025581</v>
+        <v>-0.001040373455890529</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.09055639195969721</v>
+        <v>-0.04006247242218285</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.09510681464488419</v>
+        <v>0.1291340622820831</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.02850717404708407</v>
+        <v>-0.01070710901300435</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02400549711414315</v>
+        <v>0.03375554635893488</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0.1348950075532094</v>
+        <v>-0.01483435308478475</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,79 +2057,79 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.0159832680812507</v>
+        <v>-0.0003429861718868228</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.1106374971742739</v>
+        <v>0.1502529154334531</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1663901592560021</v>
+        <v>0.1139005617207824</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.06743722634934957</v>
+        <v>0.1173771491392673</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.01400271525306769</v>
+        <v>0.1685094567752499</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.03842259128365399</v>
+        <v>-0.07259784723097416</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1548446957747366</v>
+        <v>0.1563635426019329</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0.05501837652056594</v>
+        <v>-0.05229758479383485</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.07907260673471657</v>
+        <v>0.111212244162719</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.149614151132719</v>
+        <v>0.1091790759481127</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0.01912422175192491</v>
+        <v>0.06791816624839057</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1456839211514797</v>
+        <v>0.00101565619207446</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007019995131012038</v>
+        <v>3.876961786800372e-05</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0348560714663351</v>
+        <v>-8.283898390000788e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,25 +3305,25 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1612515046311658</v>
+        <v>0.002421666249955447</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008919166770398279</v>
+        <v>-3.038023390619159e-05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.06151659595668091</v>
+        <v>-0.0004648570262004973</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,49 +3332,49 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1059754179018192</v>
+        <v>0.0006710002019465617</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1293372633758022</v>
+        <v>-0.002041613223024548</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.01137106196058207</v>
+        <v>-0.0003715763334996888</v>
       </c>
       <c r="Z6" t="n">
         <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05036791138715228</v>
+        <v>-0.0001749233593741056</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.003017014811925896</v>
+        <v>-0.0003568253690801718</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006116257423711823</v>
+        <v>-0.0001282064406515761</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3383,10 +3383,10 @@
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0378211119425077</v>
+        <v>0.0006343760843263322</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,52 +3395,52 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.05468071147151903</v>
+        <v>0.0002812771096520189</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.05253515466430465</v>
+        <v>-0.0003960821243699694</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3152710242283234</v>
+        <v>0.005168650793937381</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2723810703161728</v>
+        <v>-0.0007826635889328851</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.13288205426974</v>
+        <v>-0.0003164691345037652</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02096342756028269</v>
+        <v>-0.001043478885405898</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1150222220297042</v>
+        <v>-0.0007975253725578159</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.008249788287343436</v>
+        <v>0.0001542353244151424</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.09813345969390337</v>
+        <v>0.001866348432508579</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.06747357917422028</v>
+        <v>0.002274456622518244</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.08091866198941465</v>
+        <v>-0.001121525825225353</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,34 +3494,34 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1541422805246134</v>
+        <v>0.002777834883320566</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1269486415455983</v>
+        <v>-0.0007118173316858089</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.06821928795145235</v>
+        <v>0.0001624085303218192</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.09930064298814943</v>
+        <v>-0.0006017440772122843</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,16 +3530,16 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00775702566304565</v>
+        <v>-0.0002287296490698349</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.03800833397579291</v>
+        <v>0.0002874404129750098</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,34 +3548,34 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001606455925646153</v>
+        <v>-0.0006316543342640103</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.03097985535778277</v>
+        <v>0.0002410832136143954</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.007224657393728026</v>
+        <v>1.274848856311575e-05</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1086954120369406</v>
+        <v>-0.0007176002367612514</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
@@ -3584,13 +3584,13 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.03038566501797262</v>
+        <v>-0.0004143067669859706</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.04596778765785167</v>
+        <v>0.0004708884045853199</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.06699575927271648</v>
+        <v>-0.002025373700656727</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08222163819467267</v>
+        <v>-0.001712479402524628</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.03751528662767125</v>
+        <v>-6.135208384709953e-05</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
@@ -3626,25 +3626,25 @@
         <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0006778493548603449</v>
+        <v>-0.0004856218338922727</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.05610061857016682</v>
+        <v>-0.000117460898953707</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01308885959260702</v>
+        <v>0.00174102059815628</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3656,34 +3656,34 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.141000031011637</v>
+        <v>-0.0002113110594584764</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02517172784887232</v>
+        <v>-0.001514234959018723</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.02518934955743813</v>
+        <v>0.0005523637327720214</v>
       </c>
       <c r="ED6" t="n">
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.07731268723237493</v>
+        <v>-0.0006755023650128138</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,16 +3692,16 @@
         <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.03393434822428795</v>
+        <v>-0.000451153459559144</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.056092974539629</v>
+        <v>-0.0001431979925361142</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.07831623332410131</v>
+        <v>-9.223399975444112e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.1112028557580193</v>
+        <v>0.0003337774603431214</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.02631446050626329</v>
+        <v>0.0009483441423234984</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,10 +3734,10 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1085796861599142</v>
+        <v>-0.001222747256899893</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,13 +3746,13 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.04688224056743139</v>
+        <v>-0.000429930971623891</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.04758816507193727</v>
+        <v>0.0004042188807369086</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3764,7 +3764,7 @@
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.004902250625741452</v>
+        <v>0.001026503194803009</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,70 +3773,70 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.07309690290363155</v>
+        <v>-0.0005174968822968145</v>
       </c>
       <c r="FL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0.00637798316184528</v>
+        <v>-1.402995261780974e-06</v>
       </c>
       <c r="FN6" t="n">
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01233943440136476</v>
+        <v>1.482429379424689e-05</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001688817940660875</v>
+        <v>0.0003767929916280551</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0383181622230787</v>
+        <v>-0.0002811227934271415</v>
       </c>
       <c r="FW6" t="n">
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.05905891350312934</v>
+        <v>-0.0007088385248575894</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
-        <v>-0.03573465439756787</v>
+        <v>0.0006715916322775564</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG6" t="n">
         <v>-0</v>
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.308136041568655</v>
+        <v>0.4680135213328546</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.246979541901954</v>
+        <v>-0.249484502375724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001418305825317624</v>
+        <v>0.0006948715989825681</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2820396920712785</v>
+        <v>0.5893300186197082</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1898442081304796</v>
+        <v>-0.2376903082257765</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04438314547111684</v>
+        <v>-0.07407027648037866</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,22 +4470,22 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1863711960531554</v>
+        <v>0.3188882536532863</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.03245113711132101</v>
+        <v>-0.06518635726110371</v>
       </c>
       <c r="W8" t="n">
-        <v>0.145548781867915</v>
+        <v>0.01075425273665464</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -4494,28 +4494,28 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03480821812840731</v>
+        <v>-0.03298408473697743</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.002781491789784687</v>
+        <v>0.1458752589810768</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.009919946858551429</v>
+        <v>-0.02541284935582946</v>
       </c>
       <c r="AG8" t="n">
         <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -4524,43 +4524,43 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.03767580068383242</v>
+        <v>0.3185415225150591</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.09125961872095562</v>
+        <v>-0.1886198107270233</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.06676844220371166</v>
+        <v>0.2649094524467833</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5489202953699498</v>
+        <v>0.8543505013760248</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.1290745349497014</v>
+        <v>-0.411010394584692</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1636374207254766</v>
+        <v>-0.2486532626035955</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4569,25 +4569,25 @@
         <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0561073505034549</v>
+        <v>-0.01150079128210187</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1272971252237194</v>
+        <v>-0.1590433572063247</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1179612876189809</v>
+        <v>-0.1256984815331091</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4605,16 +4605,16 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.05334062555852546</v>
+        <v>-0.116222839428088</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0532781039061477</v>
+        <v>0.04570715386983926</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1882309561883448</v>
+        <v>0.06005063771948244</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4632,16 +4632,16 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2680978234446056</v>
+        <v>0.7314189974110187</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.05079859067566444</v>
+        <v>-0.2054143979684063</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.1276664921846821</v>
+        <v>0.01227499292435315</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -4650,31 +4650,31 @@
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.1224368969974488</v>
+        <v>-0.3353566217177941</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.05188857132559846</v>
+        <v>0.2587892856792918</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.03454128338347627</v>
+        <v>-0.08663755705216339</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,49 +4686,49 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.00398082907903584</v>
+        <v>-0.1975366409507522</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.06933921517193167</v>
+        <v>0.3666171375945244</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.0810868990527604</v>
+        <v>0.09917944216406015</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1156062459157742</v>
+        <v>-0.3373041944074143</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.08205920303793832</v>
+        <v>0.2501803921340847</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.03955027220541803</v>
+        <v>-0.05785004250337372</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,46 +4740,46 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.1128934867186368</v>
+        <v>-0.5069218621652868</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.04399754718010405</v>
+        <v>0.1386554424265235</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.05508072600522133</v>
+        <v>-0.09345930652115762</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.01308922988748438</v>
+        <v>-0.1074132598729806</v>
       </c>
       <c r="DP8" t="n">
         <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.08704078079537347</v>
+        <v>0.07242624325862036</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.1098382042861213</v>
+        <v>0.003328859883093331</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4794,25 +4794,25 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.04924936518695596</v>
+        <v>0.1092378561718847</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.0311825530133635</v>
+        <v>-0.2776010064695211</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03246154201041541</v>
+        <v>-0.2847400710678546</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,22 +4821,22 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1058295024999718</v>
+        <v>-0.3027354151073762</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.07708542364148763</v>
+        <v>0.2134120341277718</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.05794504266960257</v>
+        <v>-0.01748315027900779</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,25 +4845,25 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.1396256541959134</v>
+        <v>-0.2236461961291064</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.06232282006589054</v>
+        <v>0.06915527532765653</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02467415193067227</v>
+        <v>0.01946410205850446</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4872,25 +4872,25 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1209171992911096</v>
+        <v>-0.4019723485871931</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05664225252624153</v>
+        <v>0.3151540098875595</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03895755471164623</v>
+        <v>-0.080904754107667</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4899,49 +4899,49 @@
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03402184132564226</v>
+        <v>-0.2501276305276404</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.09382094824954623</v>
+        <v>0.1725638213341054</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.01860101454586399</v>
+        <v>0.02014947461920463</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02151819083240892</v>
+        <v>-0.05391067501886608</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.07911482123993194</v>
+        <v>0.1585738216096483</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.005858280160383282</v>
+        <v>0.03324205013323243</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
         <v>0</v>
@@ -4953,28 +4953,28 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.04637325522405137</v>
+        <v>-0.3808290367061347</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.1171996280644711</v>
+        <v>0.1442058248352464</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2553323292486331</v>
+        <v>0.476492105399981</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06035569036219256</v>
+        <v>0.0140547868978985</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1405023945453774</v>
+        <v>-0.1225296311014108</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,25 +5012,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1963461923007995</v>
+        <v>0.6188913633125106</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04421655169414063</v>
+        <v>-0.1009640950618155</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2470126368590713</v>
+        <v>-0.1432426776682864</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08151067089495979</v>
+        <v>0.1708751561789835</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,64 +5048,64 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06290113827107999</v>
+        <v>-0.1303637369365144</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02800001905935462</v>
+        <v>-0.0387503622811611</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01989540174974715</v>
+        <v>0.01210480274458175</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01308862025146248</v>
+        <v>-0.0643734057630875</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004597412030669789</v>
+        <v>-0.05142357542033883</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07498654663952052</v>
+        <v>0.2655264258863291</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.004162330227686552</v>
+        <v>0.1976583155090205</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.09621699459964303</v>
+        <v>-0.2520540588974006</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5117,37 +5117,37 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.3810597779702696</v>
+        <v>1.053481743331629</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1339831952535404</v>
+        <v>-0.2871762390817434</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.2984109151148688</v>
+        <v>-0.3004833718961756</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.09382221172000745</v>
+        <v>-0.003713678728142966</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07930957121456964</v>
+        <v>-0.08913769400614485</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.05496398359694169</v>
+        <v>-0.1097176741850608</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.09085908738331115</v>
+        <v>0.01243717642068739</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.005913677274176876</v>
+        <v>0.1822985436784725</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01648157093132357</v>
+        <v>0.02759170752917412</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1748125593362344</v>
+        <v>0.7190990604342494</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.09986797577448973</v>
+        <v>-0.1176140074313322</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.1215082261820448</v>
+        <v>-0.2358161497799062</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,67 +5222,67 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.09444803992882324</v>
+        <v>-0.3277859396173685</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01186001075146671</v>
+        <v>-0.007100769985337612</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1035957028969557</v>
+        <v>0.1643421886563396</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.0002878623807203</v>
+        <v>-0.2684713821919001</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.02942368232175689</v>
+        <v>0.1200566679299594</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.005337961829377705</v>
+        <v>0.1881780249046533</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.07921731318496898</v>
+        <v>-0.3246944754597573</v>
       </c>
       <c r="CX9" t="n">
         <v>-0</v>
@@ -5291,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.005785932381349564</v>
+        <v>-0.03104865237890815</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1187519738825575</v>
+        <v>0.1453030851360523</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.0238254309452103</v>
+        <v>-0.04320787395201089</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
@@ -5318,43 +5318,43 @@
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.06375818220772057</v>
+        <v>-0.2940009970660832</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.06245362777140466</v>
+        <v>0.04295210393743862</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.007144762344660035</v>
+        <v>-0.1405159963822276</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02002437030255545</v>
+        <v>-0.00586608528677242</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.01367269124875494</v>
+        <v>0.02122720085642914</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,19 +5363,19 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.05682305866219151</v>
+        <v>0.07764953988764782</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01998850327167285</v>
+        <v>-0.05785102285102073</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.08184701509984406</v>
+        <v>-0.1541061029992307</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
@@ -5387,22 +5387,22 @@
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.074837383831558</v>
+        <v>-0.06773138121605939</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.01914074450782193</v>
+        <v>-0.1119831007122527</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.1128541724024182</v>
+        <v>0.03538139899119523</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
@@ -5414,103 +5414,103 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02950308962608741</v>
+        <v>-0.1755185101552535</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02162450000639929</v>
+        <v>-0.2244022078820907</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.04860572160368239</v>
+        <v>0.07093507040352207</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.07519737562396658</v>
+        <v>-0.3545262251366729</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.003634813535722961</v>
+        <v>-0.05596250195159911</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.1034465240717119</v>
+        <v>0.1361125386945142</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.04531451440036609</v>
+        <v>-0.367828062792797</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03193724451937031</v>
+        <v>0.1327007502482133</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.08666481688870464</v>
+        <v>0.1595727133736484</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.01582527408402181</v>
+        <v>-0.08336369006428532</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.01524935124616478</v>
+        <v>0.02425516918040202</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.07052617018832834</v>
+        <v>0.1517850994021259</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,13 +5522,13 @@
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.003380327058767873</v>
+        <v>-0.1005765093146997</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.05527249178258466</v>
+        <v>-0.08494520331526866</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1033987582074574</v>
+        <v>0.01444202208378105</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,34 +6132,34 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06180872139991046</v>
+        <v>-0.006372709700266823</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01591426624679503</v>
+        <v>0.002606077808778397</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09164053826427862</v>
+        <v>0.01764586628574095</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04905786988559949</v>
+        <v>-0.0119962733022142</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6168,16 +6168,16 @@
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.04879486110389886</v>
+        <v>0.001277480163123275</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1012258459267559</v>
+        <v>0.01038754458324826</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02310199215796888</v>
+        <v>-0.01304183918353601</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,79 +6195,79 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.0408153618320814</v>
+        <v>-0.003618570533686965</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02288544059169746</v>
+        <v>0.0003301335320383845</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02311497268495512</v>
+        <v>-0.004105591911703655</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.002819277496495619</v>
+        <v>0.002690385125179365</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05190999538630606</v>
+        <v>0.01116645456102967</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02447071518995486</v>
+        <v>-0.004047152028375867</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.02637654038119692</v>
+        <v>0.002782815559263653</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2566512383833651</v>
+        <v>0.04034155121685012</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03413403374083424</v>
+        <v>-0.02083606486236421</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6276,7 +6276,7 @@
         <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.05089016452021177</v>
+        <v>-0.0001685378131255292</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.0363734537201918</v>
+        <v>-0.007451692579979107</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,25 +6294,25 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1036487993020915</v>
+        <v>-0.01124972975750465</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-0.05424439728912034</v>
+        <v>0.0009699543218663041</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06241268488734149</v>
+        <v>0.01429020094660464</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,43 +6321,43 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02984530240879427</v>
+        <v>0.009553680441010362</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.008823618188773162</v>
+        <v>-0.002919646762520154</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.158269913482134</v>
+        <v>0.02694688679624492</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01880301415026433</v>
+        <v>-0.01219962595645383</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.03197641412843023</v>
+        <v>-0.003699113049723575</v>
       </c>
       <c r="CC11" t="n">
         <v>-0</v>
@@ -6366,7 +6366,7 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03822577257145659</v>
+        <v>-0.005746507892048934</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
@@ -6375,52 +6375,52 @@
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0190978413591189</v>
+        <v>0.004232496154110127</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.002160569622381371</v>
+        <v>-0.00124942777078826</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02253269881005172</v>
+        <v>-0.007117947966358638</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04403029298305127</v>
+        <v>0.01183848548930854</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0008816007444548573</v>
+        <v>0.003109681383246473</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02673163825032252</v>
+        <v>-0.005271136139131917</v>
       </c>
       <c r="CX11" t="n">
         <v>0</v>
@@ -6429,43 +6429,43 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.004963392188269864</v>
+        <v>0.003866772368234405</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0.002630574243376753</v>
+        <v>0.0006580641554077552</v>
       </c>
       <c r="DD11" t="n">
         <v>-0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.120113232045637</v>
+        <v>0.001514877196155079</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01277067501244165</v>
+        <v>-0.00384817396506892</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.01459758004107834</v>
+        <v>-0.0004909382858904396</v>
       </c>
       <c r="DM11" t="n">
         <v>-0</v>
@@ -6474,7 +6474,7 @@
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.005541938693666868</v>
+        <v>-0.009047138000656868</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,43 +6483,43 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.006566740069972578</v>
+        <v>-0.003037112837820344</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0.01689898466044384</v>
+        <v>0.003521208797200295</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.04715619769001198</v>
+        <v>0.005289282365695973</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.04924664737267104</v>
+        <v>-0.01049372840856284</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.009089230947277914</v>
+        <v>-0.005104449005696489</v>
       </c>
       <c r="EE11" t="n">
         <v>0</v>
@@ -6528,16 +6528,16 @@
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.007932857724687221</v>
+        <v>0.0002063522865280001</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.03575489206650671</v>
+        <v>-0.005077271736875233</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6546,43 +6546,43 @@
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.02529207986816507</v>
+        <v>-0.001289140445110197</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.05818188113843341</v>
+        <v>0.0005232747350789701</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01706992689060513</v>
+        <v>-0.002090253073304271</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.04654975367123194</v>
+        <v>-0.0001602661061294353</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.03345131591073507</v>
+        <v>-0.007304898864355134</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.002186820400608861</v>
+        <v>0.002823312822479594</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001980597510450248</v>
+        <v>0.0006007753049418192</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.03030582885566441</v>
+        <v>0.001040240035506305</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01474060629656515</v>
+        <v>0.007280243878984505</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0.03143877613056822</v>
+        <v>-0.009332995058960163</v>
       </c>
       <c r="FO11" t="n">
         <v>-0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001465884914252954</v>
+        <v>-0.001065802677524361</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,28 +6645,28 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.005081431625724553</v>
+        <v>0.002200834181319083</v>
       </c>
       <c r="FU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0.01651565299580694</v>
+        <v>0.0002907606290217093</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.06352783391278963</v>
+        <v>-0.005721482724779755</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
@@ -6675,13 +6675,13 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0.03330224257608763</v>
+        <v>-0.003378543368922086</v>
       </c>
       <c r="GG11" t="n">
         <v>-0</v>
@@ -6689,19 +6689,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.1129286508972713</v>
+        <v>-0.04964802002669524</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3934606958369784</v>
+        <v>0.07275673683715357</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1205523579464054</v>
+        <v>-0.02200307713012989</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6716,91 +6716,91 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06755002786734846</v>
+        <v>-0.03577376604973211</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2559820835806024</v>
+        <v>0.08356688250007063</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1800152427255538</v>
+        <v>-0.02579302254368446</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01623293358140101</v>
+        <v>0.01468003042723692</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2671674238197894</v>
+        <v>0.01123473141545783</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05303149412720707</v>
+        <v>-0.0009956596072438725</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.920768793610937e-11</v>
+        <v>-2.860500386986701e-12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03921351927060709</v>
+        <v>0.002106912123971353</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.0003379980955681565</v>
+        <v>-0.004300003081365542</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.06806368198932924</v>
+        <v>-0.004587767894531822</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.2089998724990556</v>
+        <v>0.03330645312320941</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -6809,52 +6809,52 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.05737450468985338</v>
+        <v>-0.007081018326720091</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.09071032357272926</v>
+        <v>-0.01579562547720512</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.541667417840325</v>
+        <v>0.0829297326132057</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1617179785343792</v>
+        <v>-0.047224109377603</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.05722529226282546</v>
+        <v>-0.04115212416409791</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.04634216462226342</v>
+        <v>0.01260427884480699</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.3282327371717088</v>
+        <v>-0.01713676242388487</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.005689404964449868</v>
+        <v>0.01202441888059377</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.02899987122844675</v>
+        <v>0.02051448575655197</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.06134513232691902</v>
+        <v>0.04468013579052404</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6905,10 +6905,10 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08185553423724622</v>
+        <v>0.0004013815268035167</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4141928545992247</v>
+        <v>0.07216927596852178</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,52 +6917,52 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01895599535333535</v>
+        <v>-0.01422802444566506</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.03608559607893798</v>
+        <v>0.02862904698511616</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1042034095633602</v>
+        <v>-0.03794383135620361</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.003311361857313077</v>
+        <v>0.0008801322124160736</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.09765670836580827</v>
+        <v>0.007790452932302053</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.008757178829219758</v>
+        <v>-0.03069467210320854</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06049236545915489</v>
+        <v>0.002129376135152895</v>
       </c>
       <c r="CR12" t="n">
         <v>-0</v>
@@ -6983,121 +6983,121 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.01867878896234685</v>
+        <v>0.02591904748492205</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1128188374858225</v>
+        <v>-0.03822329516085848</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.004028395428125664</v>
+        <v>-0.002379805447057993</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.04992623904213585</v>
+        <v>0.01096033490386043</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.1971872018027434</v>
+        <v>-0.05860883892634262</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08017515092536989</v>
+        <v>-0.02140967540353253</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0.07613377232160144</v>
+        <v>-0.01737084236476124</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07353923112270259</v>
+        <v>-0.02833085339559912</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01599533748582309</v>
+        <v>0.0001510358237184629</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0.03631876443315511</v>
+        <v>0.006709813189988085</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1084951974620932</v>
+        <v>0.01280862712365495</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.08717166272743332</v>
+        <v>0.02322241762389409</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.01235817142517943</v>
+        <v>0.01806544303287232</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.03440654406264015</v>
+        <v>-0.01395451907637029</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
@@ -7106,34 +7106,34 @@
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.008907800445750657</v>
+        <v>-0.01243226492569876</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.004399102494548317</v>
+        <v>0.0117471549540659</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1047370057322039</v>
+        <v>-0.01847266298771004</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01914548170946802</v>
+        <v>-0.007174946101795729</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
@@ -7145,13 +7145,13 @@
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.01485141860426576</v>
+        <v>0.03162373625837871</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1182367563524874</v>
+        <v>-0.04666858508420466</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.03319979597720287</v>
+        <v>-0.003532538607794533</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,10 +7175,10 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.04879575787577533</v>
+        <v>0.02054990191291621</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.05408039401192199</v>
+        <v>-0.02606199457220477</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,7 +7187,7 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.08793089961423908</v>
+        <v>0.02227614768801659</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7196,31 +7196,31 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>-0.04258302787323238</v>
+        <v>0.003674797648748396</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03929665386912452</v>
+        <v>0.004751186228594659</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.008417817807125007</v>
+        <v>0.008121243312028565</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
@@ -7229,10 +7229,10 @@
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0.07957161118919936</v>
+        <v>0.02533419125468746</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.05231683463534471</v>
+        <v>-0.02048470848906481</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
@@ -7244,42 +7244,42 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3415514966458008</v>
+        <v>0.003263200021833188</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.05987241321972574</v>
+        <v>-0.001412162987328054</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1212770365090693</v>
+        <v>-0.001094455616842419</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1970972272572605</v>
+        <v>0.004278661083993044</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0767720471228422</v>
+        <v>-0.001239967109419061</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.09026116686894002</v>
+        <v>-0.001396814853290077</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,88 +7315,88 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1369491858146346</v>
+        <v>0.0004449900704951245</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.09772895390758969</v>
+        <v>-0.00120023325043483</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.02960401965795932</v>
+        <v>-2.438799445941941e-05</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04379197919354457</v>
+        <v>-6.085828079589141e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00586778757728071</v>
+        <v>-0.0001870903348053988</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.436090362232546e-13</v>
+        <v>-1.003998667386854e-13</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08414764576320176</v>
+        <v>0.001296218066149037</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.03063664236672827</v>
+        <v>8.20977109029349e-05</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.06961103336264543</v>
+        <v>-0.0003436165770563132</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4720946925883336</v>
+        <v>0.006203708193188557</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,25 +7405,25 @@
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.08259717405793482</v>
+        <v>-0.0006798858298965668</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.08382232692156831</v>
+        <v>-0.0005658915415701108</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0654141966932334</v>
+        <v>-0.001662361705328776</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.146005208341475</v>
+        <v>-0.001260836776935403</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.07095597978758073</v>
+        <v>-0.0002502144081304155</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
@@ -7447,10 +7447,10 @@
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.002366086193398574</v>
+        <v>0.0004776535128884942</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,13 +7459,13 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.07367222442108862</v>
+        <v>0.003195063051729583</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.05709567735314711</v>
+        <v>0.0003377438537357188</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,49 +7477,49 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2152668213115117</v>
+        <v>0.004080946404936055</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.01421893667494718</v>
+        <v>-0.0008107023011237614</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0.04919836208327753</v>
+        <v>-0.000239207726310208</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1056656352745827</v>
+        <v>-0.001778310675747451</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.003337534779917592</v>
+        <v>0.000676097378468196</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.04178483193514076</v>
+        <v>0.0002687924154071556</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
@@ -7528,25 +7528,25 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.0452389736237582</v>
+        <v>-0.001304509211734323</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04502092263144209</v>
+        <v>2.490503316335736e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.005738084025857479</v>
+        <v>-0.0005600950689518461</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,25 +7555,25 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.09908585918659761</v>
+        <v>-0.001885927943950561</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.006238431709342388</v>
+        <v>0.0004119987969586555</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.04711285676169643</v>
+        <v>0.000554196998622302</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.2329864090880344</v>
+        <v>-0.0009869875131525753</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,52 +7594,52 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05570608745279546</v>
+        <v>-0.0007920196718365268</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0.03480049417973468</v>
+        <v>-0.0005716246651952127</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.007059779686927379</v>
+        <v>-0.0008455344497932298</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01393395898694593</v>
+        <v>1.608484109150447e-05</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01177372856978751</v>
+        <v>0.0006192305507294235</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.08280815804559229</v>
+        <v>0.001624021134635357</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.03190468650863516</v>
+        <v>-0.0004517927881252135</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.008062422711113466</v>
+        <v>0.0003567989878058162</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7663,25 +7663,25 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.04472951453214273</v>
+        <v>-0.001275468338187074</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03147638773710253</v>
+        <v>0.0004167386312750419</v>
       </c>
       <c r="EK13" t="n">
         <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.03671949032698358</v>
+        <v>-0.0002301688936515398</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7693,49 +7693,49 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.07473376487879467</v>
+        <v>-0.0009862032585248163</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.009396700169150493</v>
+        <v>1.916899001556581e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0.00909030006615771</v>
+        <v>-0.0002013352295834757</v>
       </c>
       <c r="EV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1058395788155789</v>
+        <v>-0.002081906996597658</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02131028776560923</v>
+        <v>0.0002254691104629734</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.04672113474762873</v>
+        <v>0.0002904969834255447</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7744,37 +7744,37 @@
         <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.06680534733891758</v>
+        <v>-0.0001027586418989578</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06208347784782419</v>
+        <v>0.0002940659381072231</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.03119152395862422</v>
+        <v>-9.640650091458512e-05</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.0149767313261869</v>
+        <v>8.454562650820726e-05</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,46 +7783,46 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.005232407404600471</v>
+        <v>0.0003088788178066462</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.06150084433315758</v>
+        <v>0.0005562330752855004</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.06988852365815514</v>
+        <v>-0.001632384969930132</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0.07037210843434419</v>
+        <v>0.0005210386418261319</v>
       </c>
       <c r="GF13" t="n">
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4940848067229939</v>
+        <v>0.995290080643652</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1556707240961142</v>
+        <v>-0.3386024244867957</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,13 +7851,13 @@
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2113018654625718</v>
+        <v>-0.1970460224280068</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3077829916219924</v>
+        <v>1.11866969011118</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1810962509662244</v>
+        <v>-0.3215330411345179</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7875,28 +7875,28 @@
         <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1699307642707485</v>
+        <v>-0.1141583104316127</v>
       </c>
       <c r="S14" t="n">
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1908462999132181</v>
+        <v>0.2094152469073502</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03915750965719401</v>
+        <v>-0.3149587140942211</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7905,76 +7905,76 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.05363557702180044</v>
+        <v>-0.2626946507475998</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.05163563972683565</v>
+        <v>0.03628305723471912</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.008129089255700274</v>
+        <v>-0.09244831026828855</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.002825772657178147</v>
+        <v>0.003414730807995887</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.1210527973473092</v>
+        <v>0.4804514598714231</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.01626450935588715</v>
+        <v>0.2246096327506148</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0.05341220890147508</v>
+        <v>-0.08257838290080027</v>
       </c>
       <c r="AT14" t="n">
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.6003596630656459</v>
+        <v>1.722328570109727</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1010110057600429</v>
+        <v>-0.2415799821541386</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.1759626023047828</v>
+        <v>0.003101508031208537</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.1065828136399348</v>
+        <v>-0.3189351353397684</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,25 +8001,25 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.2895850914223399</v>
+        <v>-0.329805551246225</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0.1445764838589528</v>
+        <v>-0.148334425098925</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.04551499332200066</v>
+        <v>0.08587882366798372</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
@@ -8028,52 +8028,52 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.2156227848496671</v>
+        <v>0.2109474092626598</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.003010156642644035</v>
+        <v>0.1210929559773549</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.3520641780971481</v>
+        <v>1.122239709309238</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.01571103973742782</v>
+        <v>-0.2470389926085048</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0.06497944448137635</v>
+        <v>-0.2586083576175648</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.148330876035297</v>
+        <v>-0.5731976778320858</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
@@ -8082,25 +8082,25 @@
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.005980381114792039</v>
+        <v>0.1152266859092199</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.09949941009239956</v>
+        <v>0.09239202183056749</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.07953155588326682</v>
+        <v>-0.4380477897575068</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,7 +8109,7 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.04418803264317025</v>
+        <v>0.07772828407158222</v>
       </c>
       <c r="CR14" t="n">
         <v>-0</v>
@@ -8121,40 +8121,40 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.02080527379596706</v>
+        <v>0.06234856121082344</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1306142630132254</v>
+        <v>-0.5604319643372065</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.005735740808937768</v>
+        <v>0.07676561026125377</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0776680065575049</v>
+        <v>0.1592129285231625</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.1850186325087347</v>
+        <v>-0.2101157999249314</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
@@ -8163,7 +8163,7 @@
         <v>-0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01884111295873396</v>
+        <v>0.07071867016894146</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8172,25 +8172,25 @@
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.001501331977913584</v>
+        <v>-0.1532693212302406</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.01863234106622962</v>
+        <v>-0.3059702004530451</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.007528892375356588</v>
+        <v>0.06451707767798448</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,124 +8199,124 @@
         <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0.006425750067442979</v>
+        <v>-0.1641904130437563</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.1032443968463352</v>
+        <v>0.3554681130223526</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.04373245824401272</v>
+        <v>-0.221803979232642</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0.0002569892388709924</v>
+        <v>0.1650680426321778</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.05482021241611838</v>
+        <v>-0.2839482307386916</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.02420375537790847</v>
+        <v>-0.07054136692571045</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.1284321881389089</v>
+        <v>0.08918931591954808</v>
       </c>
       <c r="EO14" t="n">
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.1244504007755015</v>
+        <v>-0.3319898509061475</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02418958060514468</v>
+        <v>-0.01316936852033992</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.07087522938713864</v>
+        <v>0.1763449729358031</v>
       </c>
       <c r="EX14" t="n">
         <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1516891220406906</v>
+        <v>-0.6425159998183254</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.009147080558182901</v>
+        <v>0.06258087688150642</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.07867804424159633</v>
+        <v>0.1479470178511783</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.08670814401796181</v>
+        <v>-0.218593508678428</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,25 +8325,25 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.06410916916761182</v>
+        <v>-0.08988400153587048</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0.0357218924941721</v>
+        <v>-0.1810261776445644</v>
       </c>
       <c r="FP14" t="n">
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.02463184115138704</v>
+        <v>-0.0536352339085876</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,7 +8352,7 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.00612399302497947</v>
+        <v>0.03479896230721768</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,37 +8361,37 @@
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.006005854261766714</v>
+        <v>-0.1513887748915959</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.1043109663002531</v>
+        <v>-0.2731236013876229</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0.02146843487910407</v>
+        <v>0.1677956765796951</v>
       </c>
     </row>
     <row r="15">
@@ -8968,16 +8968,16 @@
         <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4408189616825194</v>
+        <v>-0.6324741728496693</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4857436483879309</v>
+        <v>0.2298237636761775</v>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001208377023675562</v>
+        <v>0.2667902740872209</v>
       </c>
       <c r="F16" t="n">
         <v>-0</v>
@@ -8995,25 +8995,25 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3087116600858973</v>
+        <v>-0.7306281460809427</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3583905892554451</v>
+        <v>0.1839908134131542</v>
       </c>
       <c r="M16" t="n">
         <v>-0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2090874964937682</v>
+        <v>0.1842316164640409</v>
       </c>
       <c r="O16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R16" t="n">
         <v>-0</v>
@@ -9022,16 +9022,16 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1268263960429287</v>
+        <v>-0.2024983850760656</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01122975220054954</v>
+        <v>-0.1280954560477353</v>
       </c>
       <c r="V16" t="n">
         <v>-0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.04769217841188785</v>
+        <v>-0.08223350024899811</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -9040,106 +9040,106 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.08555077676928874</v>
+        <v>-0.01242288911682277</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.0002111815623978148</v>
+        <v>0.1042626153631848</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0525606753191706</v>
+        <v>0.03696145080935544</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.2448814962092515</v>
+        <v>-0.3394616700582709</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.06792721213575587</v>
+        <v>0.03080804717162754</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01444006519919969</v>
+        <v>-0.3582124039464906</v>
       </c>
       <c r="AP16" t="n">
         <v>-0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.4669255449430049</v>
+        <v>-0.9722063523476022</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.339746320626391</v>
+        <v>-0.05297208552640742</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1471355699317606</v>
+        <v>-0.04187268178789373</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.08600552547067963</v>
+        <v>0.3804047743587684</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.174965901881208</v>
+        <v>0.2585668762033214</v>
       </c>
       <c r="BF16" t="n">
         <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.376822756907503</v>
+        <v>0.5489031637523909</v>
       </c>
       <c r="BH16" t="n">
         <v>-0</v>
@@ -9157,25 +9157,25 @@
         <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0.05125753107376308</v>
+        <v>0.08455707552803057</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.08945819751303594</v>
+        <v>0.01302817136672182</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.1183041894332046</v>
+        <v>-0.0312102777248937</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
         <v>0</v>
@@ -9184,19 +9184,19 @@
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>-0.1598786474952575</v>
+        <v>-0.6260802267190573</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.3386565978309464</v>
+        <v>-0.03897853354261757</v>
       </c>
       <c r="BX16" t="n">
         <v>-0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.05611973783793379</v>
+        <v>-0.07410343815232388</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>0</v>
@@ -9205,31 +9205,31 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.1349789819307364</v>
+        <v>0.3767249521069816</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.07769610865101886</v>
+        <v>-0.08658634949797006</v>
       </c>
       <c r="CG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.02440780407761631</v>
+        <v>-0.07416074391901262</v>
       </c>
       <c r="CI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,16 +9238,16 @@
         <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.02722711563298532</v>
+        <v>0.25332404324523</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.01207239363536748</v>
+        <v>-0.03490887002697092</v>
       </c>
       <c r="CP16" t="n">
         <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.09161554795852025</v>
+        <v>-0.1174541444800802</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
@@ -9262,28 +9262,28 @@
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.09908876134357367</v>
+        <v>0.3568754099481097</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.07839288106123145</v>
+        <v>-0.06631577952152855</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.004868474738878039</v>
+        <v>-0.05231102843445953</v>
       </c>
       <c r="DA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB16" t="n">
         <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>-0</v>
@@ -9292,103 +9292,103 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.1254166645390838</v>
+        <v>0.08099436724270334</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.03296181275590543</v>
+        <v>0.06846801961149111</v>
       </c>
       <c r="DH16" t="n">
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1213513130239793</v>
+        <v>0.05324418222286678</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.006497859947220424</v>
+        <v>0.1647387377302777</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0.008665938313251725</v>
+        <v>-0.07073418782533587</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.1064606393768627</v>
+        <v>-0.05583826014035247</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.06841640563289295</v>
+        <v>-0.2123021690934652</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.05709292354164554</v>
+        <v>0.006769350848660983</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.03758418037624453</v>
+        <v>0.1695609083697629</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.02205391221764075</v>
+        <v>0.2240820528617462</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0.0677272332608385</v>
+        <v>0.09737030698450033</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.06412815077385257</v>
+        <v>-0.07235632885515057</v>
       </c>
       <c r="EK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
         <v>0</v>
@@ -9397,19 +9397,19 @@
         <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.08221775854720045</v>
+        <v>0.241516139381046</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0202747506390775</v>
+        <v>0.04634692347691685</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.004297273401385887</v>
+        <v>0.01139659513300526</v>
       </c>
       <c r="ET16" t="n">
         <v>0</v>
@@ -9418,34 +9418,34 @@
         <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.1152589217846858</v>
+        <v>0.4131894743904803</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.06568982865213743</v>
+        <v>-0.07906025359711927</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.03109467287299124</v>
+        <v>-0.07309918587997978</v>
       </c>
       <c r="FC16" t="n">
         <v>0</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
         <v>0</v>
@@ -9454,19 +9454,19 @@
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.09148619382358507</v>
+        <v>0.1289955445094301</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.1221835532620295</v>
+        <v>0.2220755817463901</v>
       </c>
       <c r="FJ16" t="n">
         <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.1793878853206186</v>
+        <v>0.2119468291522048</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
         <v>-0</v>
@@ -9475,49 +9475,49 @@
         <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP16" t="n">
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>9.471605467331808e-05</v>
+        <v>0.001677743533704455</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0.05953444839317886</v>
+        <v>-0.002034845900764175</v>
       </c>
       <c r="FS16" t="n">
         <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01317976874406395</v>
+        <v>-0.02175856288938069</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
         <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.06136190134482987</v>
+        <v>0.1813175972510336</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0.001092664928008966</v>
+        <v>0.2104459475503317</v>
       </c>
       <c r="GB16" t="n">
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
         <v>0</v>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>-0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1496082658998431</v>
+        <v>0.3050360095745513</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,10 +9546,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05050764279610264</v>
+        <v>0.06400158013401473</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07783150167930862</v>
+        <v>-0.1674769457784007</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9561,10 +9561,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1084893438066814</v>
+        <v>0.3220272473673892</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,16 +9573,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0206292743286881</v>
+        <v>-0.04571577325023095</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.05058132542063425</v>
+        <v>-0.1470264742236829</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -9591,49 +9591,49 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.02334656483461089</v>
+        <v>0.1307925820487379</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.01685320739660771</v>
+        <v>-0.03629736835018972</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0005317449149046421</v>
+        <v>0.001249656014089701</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0008385756378535438</v>
+        <v>-0.01662695934095518</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.006659123548114939</v>
+        <v>-0.0568962331595159</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.003159968205281028</v>
+        <v>0.02126784312271769</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,34 +9645,34 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.02344061157875744</v>
+        <v>0.09693679564203371</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.002593447887551928</v>
+        <v>-0.03597150667206924</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.03903432690755655</v>
+        <v>-0.06297048187075689</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1136875712437861</v>
+        <v>0.5815704534895814</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.03927614719870123</v>
+        <v>-0.209841477600869</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.09202787207415655</v>
+        <v>-0.2608453366049366</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.03546575413379773</v>
+        <v>-0.1438077140173589</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,70 +9708,70 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.0357400211000821</v>
+        <v>0.002736302381433662</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.02229286350805137</v>
+        <v>-0.06537678521096568</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02482467292587764</v>
+        <v>0.1330822170123771</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>-0.002546648575107513</v>
+        <v>0.08781500073323319</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.00642027549446862</v>
+        <v>0.04154053642638391</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.06189139438839626</v>
+        <v>0.3211102710153835</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.02653877200269847</v>
+        <v>-0.0408279562914721</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.02640025337916411</v>
+        <v>-0.09459072376677409</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>-0</v>
@@ -9780,34 +9780,34 @@
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0311781498043518</v>
+        <v>-0.1293280273265344</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.001258627113071169</v>
+        <v>0.0143163492904592</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.02452932073712738</v>
+        <v>0.05694484722510691</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.005738668127066465</v>
+        <v>-0.1248799943468115</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,37 +9816,37 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.0005489756660519262</v>
+        <v>0.08676040793352575</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.01799896468366113</v>
+        <v>0.01934352001336341</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.02854765388914949</v>
+        <v>-0.121853981263481</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.003458761725712044</v>
+        <v>-0.006596791421021745</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.03034752932369078</v>
+        <v>0.09029453842520681</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9855,40 +9855,40 @@
         <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.02038873561903875</v>
+        <v>-0.1264886436581259</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04198357010656961</v>
+        <v>-0.1615775342278365</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.0009766352999453886</v>
+        <v>0.05476920091127242</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.00963550648505076</v>
+        <v>-0.08130355478301605</v>
       </c>
       <c r="DP17" t="n">
         <v>0</v>
@@ -9897,37 +9897,37 @@
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.013568503397487</v>
+        <v>0.01310651678105894</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.000199566948178412</v>
+        <v>0.08248656422432123</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.02125698854071172</v>
+        <v>-0.1140297928281721</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.007038951875142824</v>
+        <v>0.01022053976577308</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.008982954013516599</v>
+        <v>0.03711994863384966</v>
       </c>
       <c r="EC17" t="n">
         <v>0</v>
@@ -9936,25 +9936,25 @@
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
         <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.03249091348122058</v>
+        <v>-0.03528280158771884</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
         <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.01244890074491323</v>
+        <v>-0.0335965439248038</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.03448664767752143</v>
+        <v>-0.03569887343870646</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
@@ -9969,22 +9969,22 @@
         <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.01780821487346118</v>
+        <v>-0.01155727800894668</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.0009834098558741153</v>
+        <v>-0.08928045134940379</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.009587972805082567</v>
+        <v>-0.02867918146376466</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9996,46 +9996,46 @@
         <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.02666139601646762</v>
+        <v>-0.1514071899892321</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.003533873754926275</v>
+        <v>-0.01409304341797898</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02634767334706528</v>
+        <v>0.06864013689897967</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.001280893963123695</v>
+        <v>0.09563859468352894</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.01007008216087361</v>
+        <v>-0.03238144428424074</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.03176563858496266</v>
+        <v>0.1261001429295096</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10047,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.00281222217637857</v>
+        <v>-0.0277405752607051</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,43 +10059,43 @@
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.01125035671199754</v>
+        <v>0.05554611827105121</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01700353811588047</v>
+        <v>-0.0895617121026107</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.004676091419725967</v>
+        <v>-0.05214476896110549</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01839851382954323</v>
+        <v>0.09411891491589483</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1020841332879855</v>
+        <v>0.1526417087678394</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,40 +10115,40 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08402052929767165</v>
+        <v>-0.04405886601086263</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0169935866552945</v>
+        <v>-0.05981421938115108</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06421677013463198</v>
+        <v>0.1637992852416496</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05771565482580825</v>
+        <v>-0.07902204596326383</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.01306626349716746</v>
+        <v>-0.05600794788109285</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02156141023026783</v>
+        <v>0.06231846372131986</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -10169,37 +10169,37 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.008322170071173819</v>
+        <v>-0.05466236353752718</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01045900277248337</v>
+        <v>0.003164034593307104</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.003494791878018157</v>
+        <v>-0.02371477780636356</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.003611691802032547</v>
+        <v>-0.06230904846397898</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.003468238058667024</v>
+        <v>0.00555231336475926</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -10211,28 +10211,28 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01693600797579485</v>
+        <v>0.01683485723967399</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01312647997872498</v>
+        <v>-0.0437589812754258</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01509425824321281</v>
+        <v>0.004398188360805986</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.09172262013028937</v>
+        <v>0.2074253403035326</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,10 +10250,10 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.04856937190885982</v>
+        <v>-0.1288116338023894</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.0144052958861114</v>
+        <v>-0.1069601757748156</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -10262,13 +10262,13 @@
         <v>-0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0195207084017245</v>
+        <v>-0.02065822284424913</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,64 +10277,64 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.05422323863266254</v>
+        <v>-0.01425059198536224</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.01060783340913262</v>
+        <v>-0.01378818716350386</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.02513539238880621</v>
+        <v>0.02942306444989923</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.01462339514021655</v>
+        <v>0.06188401198311964</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0153860614232823</v>
+        <v>0.02238019032467169</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.04914350702308985</v>
+        <v>0.1248429803318388</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.02666337425894548</v>
+        <v>-0.03915003073539105</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.002590875586360009</v>
+        <v>-0.03214712190446828</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,40 +10343,40 @@
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.01814226709795432</v>
+        <v>-0.0419082847597705</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.01381361616338777</v>
+        <v>0.02690499250766374</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.006292756465611227</v>
+        <v>0.03597608880649066</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
       </c>
       <c r="CL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0003910181451737072</v>
+        <v>-0.03340721576637444</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,37 +10385,37 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.002831175779817538</v>
+        <v>0.05324666581245086</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.007262926825804069</v>
+        <v>0.02047171867909928</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01279802266547996</v>
+        <v>-0.04324501792446724</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.0122677994742888</v>
+        <v>0.02197854092911719</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.01174170143216478</v>
+        <v>0.05166613967004771</v>
       </c>
       <c r="DB18" t="n">
         <v>-0</v>
@@ -10424,25 +10424,25 @@
         <v>0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.01421292064359185</v>
+        <v>-0.04329792637302853</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.0181035049481498</v>
+        <v>-0.04405949083624984</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.00294719262654576</v>
+        <v>0.0152685473126377</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,106 +10451,106 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.004275381857019834</v>
+        <v>0.007095946239171823</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.02153534443819882</v>
+        <v>-0.02386975835392742</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.009109462437326936</v>
+        <v>-0.01317855735874414</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.01956926762507731</v>
+        <v>-0.008242463904672601</v>
       </c>
       <c r="DY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ18" t="n">
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01936645685144719</v>
+        <v>-0.003409090674396716</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.004632107804889072</v>
+        <v>0.02712466787466808</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE18" t="n">
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.02045058312696749</v>
+        <v>-0.02382702979715013</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.01249634226870981</v>
+        <v>0.01579363437080824</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.009048908578283589</v>
+        <v>0.01015815764016457</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
         <v>0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.002809502266768191</v>
+        <v>-0.02416843350541758</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.006389502698110698</v>
+        <v>0.01950102461616521</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.004764912773717733</v>
+        <v>0.05259189920909937</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
@@ -10559,25 +10559,25 @@
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.01221428599050072</v>
+        <v>-0.04862495502780667</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01293285921557576</v>
+        <v>0.01479844806877751</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.01223946426423255</v>
+        <v>0.03404565480886572</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.00403781842391285</v>
+        <v>0.05805849620830821</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,16 +10601,16 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.01522466675568582</v>
+        <v>-0.02526074963024479</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01344791572013587</v>
+        <v>0.02753451299386094</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.002808898544490414</v>
+        <v>-0.01184390393513543</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,40 +10628,40 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.00750255434764861</v>
+        <v>0.02013282042754272</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.008923002870434887</v>
+        <v>-0.05632865238998719</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.005217629771249037</v>
+        <v>-0.03858203107362491</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.008427603097652331</v>
+        <v>0.05626918471806199</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
         <v>-0</v>
@@ -10672,49 +10672,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3908482284799203</v>
+        <v>0.27906341140928</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1415305532121398</v>
+        <v>-0.1721047405623718</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.03734246700600252</v>
+        <v>-0.05382423867111009</v>
       </c>
       <c r="F19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I19" t="n">
         <v>-0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2684824886632711</v>
+        <v>0.2817095067108163</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1467026088088991</v>
+        <v>-0.2178468124267593</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05606121135248502</v>
+        <v>-0.09647993297298611</v>
       </c>
       <c r="O19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>-0</v>
@@ -10723,139 +10723,139 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1025781878612301</v>
+        <v>0.05092960879709795</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.005887372055981032</v>
+        <v>-0.03742790870700537</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1023360302370037</v>
+        <v>-0.0171264904303167</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>-0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1019684851844056</v>
+        <v>-0.004663533305219917</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.01040495651815334</v>
+        <v>-0.03984156522691736</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.003349430925435355</v>
+        <v>-0.02678072304639451</v>
       </c>
       <c r="AG19" t="n">
         <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.01435144831739498</v>
+        <v>0.05565911060018083</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.07636656378673791</v>
+        <v>-0.03304216043460818</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.08922455505332197</v>
+        <v>0.0367403440813706</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
       </c>
       <c r="AS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>-0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.3359384194582907</v>
+        <v>0.221396695599989</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>-0.07319756489617422</v>
+        <v>-0.1554939418839317</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1419134082802872</v>
+        <v>-0.1579171260080268</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
         <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
       </c>
       <c r="BC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.02797713467093448</v>
+        <v>0.002010825938985683</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.05805134466920195</v>
+        <v>-0.05721859337844349</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.1169422629402479</v>
+        <v>-0.003745060216452424</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,19 +10864,19 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.05694798247597166</v>
+        <v>0.001550845906381617</v>
       </c>
       <c r="BN19" t="n">
         <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.05899851120585817</v>
+        <v>0.07723452355695716</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1979007751952771</v>
+        <v>0.04788186151710333</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
         <v>0</v>
@@ -10885,22 +10885,22 @@
         <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
         <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.1604826507973125</v>
+        <v>0.1761781259607639</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.01855643253586027</v>
+        <v>-0.111658041366504</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.09865811961175174</v>
+        <v>-0.02389575488586959</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -10909,106 +10909,106 @@
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD19" t="n">
         <v>0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.08985607678154689</v>
+        <v>-0.07788387425564711</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.02646568059917847</v>
+        <v>0.09937519027483141</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.01216717102087097</v>
+        <v>0.01030230388279605</v>
       </c>
       <c r="CI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.02373886836111925</v>
+        <v>-0.05365453480748476</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.06123675580626253</v>
+        <v>0.1145605739243254</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1073901702012416</v>
+        <v>0.04883081840980789</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.08553426522495343</v>
+        <v>-0.08834934784503301</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.04541795342960152</v>
+        <v>0.1145525159808156</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.004737652662853742</v>
+        <v>0.01894685971002438</v>
       </c>
       <c r="DA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.01167532022366577</v>
+        <v>-0.03018910362918232</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.00522976608010529</v>
+        <v>0.02255883947343936</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.008584961919464862</v>
+        <v>-0.04433147355759415</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
@@ -11023,19 +11023,19 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.006211831031062068</v>
+        <v>-0.03911175051430004</v>
       </c>
       <c r="DP19" t="n">
         <v>0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0.1762713406829348</v>
+        <v>0.02841086132839993</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.04817659476881336</v>
+        <v>0.005100622281625763</v>
       </c>
       <c r="DS19" t="n">
         <v>-0</v>
@@ -11044,85 +11044,85 @@
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.06411067244608598</v>
+        <v>-0.02634008135294045</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.009830828483425074</v>
+        <v>0.03298517806692933</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.03959695257008852</v>
+        <v>-0.04846634956167581</v>
       </c>
       <c r="EB19" t="n">
         <v>0</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
         <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.1085980045543459</v>
+        <v>-0.0634134743568055</v>
       </c>
       <c r="EH19" t="n">
         <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.08250780357661347</v>
+        <v>0.08967125266665757</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.07410638221299015</v>
+        <v>0.02648468372586095</v>
       </c>
       <c r="EK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL19" t="n">
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.09174763403608648</v>
+        <v>-0.03152943386805694</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.08213835254051061</v>
+        <v>0.06389111200061728</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.01346117157503463</v>
+        <v>-0.0114215228907196</v>
       </c>
       <c r="ET19" t="n">
         <v>0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11134,43 +11134,43 @@
         <v>0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.08093175669359416</v>
+        <v>-0.101879262727118</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.0301811700528325</v>
+        <v>0.118328371998942</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.002043848056553023</v>
+        <v>0.01088325071226271</v>
       </c>
       <c r="FC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD19" t="n">
         <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF19" t="n">
         <v>-0</v>
       </c>
       <c r="FG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.03017341466913788</v>
+        <v>0.06845673470906528</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>-0.08295084516729991</v>
+        <v>-0.1027733631118575</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.03856790091758881</v>
+        <v>-0.004776499118770632</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11182,22 +11182,22 @@
         <v>0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.01315159667940698</v>
+        <v>-0.02651647477654762</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.1149543109851126</v>
+        <v>0.09113220629235091</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.005635113998638619</v>
+        <v>0.05896616290262913</v>
       </c>
       <c r="FU19" t="n">
         <v>-0</v>
@@ -11215,25 +11215,25 @@
         <v>-0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.0118155659803467</v>
+        <v>-0.03810200020311424</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.06156492650544612</v>
+        <v>0.05435217845283753</v>
       </c>
       <c r="GC19" t="n">
         <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
         <v>-0</v>
@@ -11813,7 +11813,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2146974991055687</v>
+        <v>0.4373872719203684</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -11822,13 +11822,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.06166249570091765</v>
+        <v>0.1166710417576716</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1372065465011049</v>
+        <v>-0.2320435110246692</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -11840,25 +11840,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1651538173850599</v>
+        <v>0.5463597474224761</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.03101471768801332</v>
+        <v>0.03738929178112004</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1097344187097961</v>
+        <v>-0.1683664257590028</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -11867,7 +11867,7 @@
         <v>-0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.02379762877177963</v>
+        <v>0.1384588586210726</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -11876,16 +11876,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.01635128109844269</v>
+        <v>-0.1191741736161786</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.004275735685908793</v>
+        <v>-0.03541747817658387</v>
       </c>
       <c r="Y21" t="n">
         <v>-0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -11894,22 +11894,22 @@
         <v>-0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.006215450076922325</v>
+        <v>0.007887111454452754</v>
       </c>
       <c r="AD21" t="n">
         <v>-0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.01330545012385246</v>
+        <v>-0.2957807775175201</v>
       </c>
       <c r="AG21" t="n">
-        <v>-7.992590638328244e-05</v>
+        <v>-0.0907955681389889</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>-0</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.03052688726185477</v>
+        <v>0.1301198132250574</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -11930,10 +11930,10 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.00331143344402303</v>
+        <v>-0.02788449165221842</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.03842386836336169</v>
+        <v>-0.09144642039184242</v>
       </c>
       <c r="AQ21" t="n">
         <v>-0</v>
@@ -11945,10 +11945,10 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.1481128656561646</v>
+        <v>0.6675610584297661</v>
       </c>
       <c r="AV21" t="n">
         <v>-0</v>
@@ -11957,25 +11957,25 @@
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>-0.02382546226205735</v>
+        <v>-0.07582594835978024</v>
       </c>
       <c r="AY21" t="n">
-        <v>-0.07844487785598281</v>
+        <v>-0.1034894064737233</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.04047987357956814</v>
+        <v>-0.09997509534723616</v>
       </c>
       <c r="BE21" t="n">
         <v>0</v>
@@ -11984,64 +11984,64 @@
         <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>-0.0547000783482053</v>
+        <v>-0.07709411701546948</v>
       </c>
       <c r="BH21" t="n">
-        <v>-0.0534923858599631</v>
+        <v>-0.133600117950018</v>
       </c>
       <c r="BI21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.03926529050770443</v>
+        <v>0.129185666080984</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO21" t="n">
         <v>-0</v>
       </c>
       <c r="BP21" t="n">
-        <v>0.0005786439610635845</v>
+        <v>0.08863890593199711</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.0195468211318834</v>
+        <v>-0.02304378903845352</v>
       </c>
       <c r="BR21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
         <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.07153860270920621</v>
+        <v>0.3680117004449046</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX21" t="n">
         <v>0</v>
       </c>
       <c r="BY21" t="n">
-        <v>-0.02562032553457219</v>
+        <v>-0.03779317210690522</v>
       </c>
       <c r="BZ21" t="n">
-        <v>-0.0493928857213525</v>
+        <v>-0.1600603324317908</v>
       </c>
       <c r="CA21" t="n">
         <v>-0</v>
@@ -12056,154 +12056,154 @@
         <v>-0</v>
       </c>
       <c r="CE21" t="n">
-        <v>-0.03638933104603533</v>
+        <v>-0.1535878669499456</v>
       </c>
       <c r="CF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG21" t="n">
         <v>-0</v>
       </c>
       <c r="CH21" t="n">
-        <v>-0.003425098364924364</v>
+        <v>0.02009266893724536</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.03078446949301888</v>
+        <v>0.09292093522574893</v>
       </c>
       <c r="CJ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK21" t="n">
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM21" t="n">
         <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>0.006472712784301688</v>
+        <v>-0.2689707929397192</v>
       </c>
       <c r="CO21" t="n">
         <v>-0</v>
       </c>
       <c r="CP21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ21" t="n">
-        <v>-0.005258313761749181</v>
+        <v>0.1314915037980961</v>
       </c>
       <c r="CR21" t="n">
-        <v>-0.01446408998899489</v>
+        <v>0.09621625686236646</v>
       </c>
       <c r="CS21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW21" t="n">
-        <v>-0.027784736787574</v>
+        <v>-0.1432577612998865</v>
       </c>
       <c r="CX21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY21" t="n">
         <v>0</v>
       </c>
       <c r="CZ21" t="n">
-        <v>-0.005347740411477608</v>
+        <v>-0.01873411204436209</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.03427269020423423</v>
+        <v>0.1186474781200755</v>
       </c>
       <c r="DB21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC21" t="n">
         <v>-0</v>
       </c>
       <c r="DD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>-0.01034246398226128</v>
+        <v>-0.05145855742107339</v>
       </c>
       <c r="DG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.02967893283345814</v>
+        <v>-0.2355266129709956</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.001847564716961329</v>
+        <v>0.05962143512777236</v>
       </c>
       <c r="DK21" t="n">
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>-0.005260052249227066</v>
+        <v>-0.05974444202084379</v>
       </c>
       <c r="DP21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ21" t="n">
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>0.02408550440186001</v>
+        <v>0.001688498373567673</v>
       </c>
       <c r="DS21" t="n">
-        <v>-0.0002697735698777041</v>
+        <v>-0.01879478202999783</v>
       </c>
       <c r="DT21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW21" t="n">
         <v>-0</v>
       </c>
       <c r="DX21" t="n">
-        <v>-0.0204188512343726</v>
+        <v>-0.06575291088250412</v>
       </c>
       <c r="DY21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ21" t="n">
         <v>-0</v>
       </c>
       <c r="EA21" t="n">
-        <v>-0.008115893331866209</v>
+        <v>-0.1893356872725337</v>
       </c>
       <c r="EB21" t="n">
-        <v>0.02432746877151867</v>
+        <v>0.08807557440103797</v>
       </c>
       <c r="EC21" t="n">
         <v>-0</v>
@@ -12215,37 +12215,37 @@
         <v>-0</v>
       </c>
       <c r="EF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG21" t="n">
-        <v>-0.03967894479605003</v>
+        <v>0.007377219792398275</v>
       </c>
       <c r="EH21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI21" t="n">
         <v>0</v>
       </c>
       <c r="EJ21" t="n">
-        <v>0.01010139768537819</v>
+        <v>-0.08259169066525363</v>
       </c>
       <c r="EK21" t="n">
-        <v>0.03197284549126673</v>
+        <v>0.005439913652093229</v>
       </c>
       <c r="EL21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM21" t="n">
         <v>-0</v>
       </c>
       <c r="EN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP21" t="n">
-        <v>-0.01394165763703744</v>
+        <v>-0.0457546644988298</v>
       </c>
       <c r="EQ21" t="n">
         <v>0</v>
@@ -12254,79 +12254,79 @@
         <v>-0</v>
       </c>
       <c r="ES21" t="n">
-        <v>-0.01371775719449716</v>
+        <v>-0.04782281586294252</v>
       </c>
       <c r="ET21" t="n">
-        <v>0.01457573055335869</v>
+        <v>0.08862605194867484</v>
       </c>
       <c r="EU21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY21" t="n">
-        <v>-0.02647403098958084</v>
+        <v>-0.169186112108647</v>
       </c>
       <c r="EZ21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA21" t="n">
         <v>-0</v>
       </c>
       <c r="FB21" t="n">
-        <v>-0.004349198245360052</v>
+        <v>-0.05256741744794888</v>
       </c>
       <c r="FC21" t="n">
-        <v>0.03124462316982133</v>
+        <v>0.1053090801395038</v>
       </c>
       <c r="FD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE21" t="n">
         <v>0</v>
       </c>
       <c r="FF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH21" t="n">
-        <v>0.0008561665074462474</v>
+        <v>0.185564864074029</v>
       </c>
       <c r="FI21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ21" t="n">
         <v>-0</v>
       </c>
       <c r="FK21" t="n">
-        <v>0.003133390353812409</v>
+        <v>-0.1469938755066164</v>
       </c>
       <c r="FL21" t="n">
-        <v>-0.02123038162692813</v>
+        <v>-0.1839214040883827</v>
       </c>
       <c r="FM21" t="n">
         <v>0</v>
       </c>
       <c r="FN21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO21" t="n">
         <v>0</v>
       </c>
       <c r="FP21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ21" t="n">
-        <v>-0.006582759523880407</v>
+        <v>-0.1150309422622585</v>
       </c>
       <c r="FR21" t="n">
         <v>-0</v>
@@ -12335,46 +12335,46 @@
         <v>-0</v>
       </c>
       <c r="FT21" t="n">
-        <v>0.003925724811692122</v>
+        <v>0.04536955963132481</v>
       </c>
       <c r="FU21" t="n">
-        <v>0.04553411504432513</v>
+        <v>-0.1387912373771158</v>
       </c>
       <c r="FV21" t="n">
         <v>-0</v>
       </c>
       <c r="FW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ21" t="n">
-        <v>0.02114471914552674</v>
+        <v>0.02789721559144994</v>
       </c>
       <c r="GA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB21" t="n">
         <v>-0</v>
       </c>
       <c r="GC21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD21" t="n">
-        <v>-0.01705513389702289</v>
+        <v>0.04492026981423372</v>
       </c>
       <c r="GE21" t="n">
         <v>-0</v>
       </c>
       <c r="GF21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
